--- a/backtest_runs/20260410_193731/by_symbol/DNCC/DNCC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DNCC/DNCC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-58.33999999998839</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>101633.52</v>
@@ -679,7 +679,7 @@
         <v>-7175.820000000002</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>94457.70000000003</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>94457.70000000003</v>
@@ -863,7 +863,7 @@
         <v>-5075.580000000005</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>89382.12000000002</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>89382.12000000002</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>89382.12000000002</v>
@@ -1139,7 +1139,7 @@
         <v>-116.6799999999975</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>94166.00000000003</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>94166.00000000003</v>
@@ -1277,7 +1277,7 @@
         <v>-9101.039999999992</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>85064.96000000004</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>85064.96000000004</v>
@@ -1415,7 +1415,7 @@
         <v>-466.7200000000004</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>84598.24000000003</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>84598.24000000003</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>84598.24000000003</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>84598.24000000003</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>84598.24000000003</v>
